--- a/Assets/06 Data/ExcelData/dt_gun_item.xlsx
+++ b/Assets/06 Data/ExcelData/dt_gun_item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\덕코프 기획\데이터테이블\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Genie\Desktop\duckov-clone\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074EE156-2AFC-4A53-9921-D8510AC52F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29524B82-8F2F-419A-8958-2DD8153567CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{818AEAD1-047B-4735-8CBD-03FE823548AF}"/>
+    <workbookView xWindow="0" yWindow="4185" windowWidth="24300" windowHeight="11295" xr2:uid="{818AEAD1-047B-4735-8CBD-03FE823548AF}"/>
   </bookViews>
   <sheets>
     <sheet name="무기" sheetId="1" r:id="rId1"/>
@@ -842,7 +842,7 @@
         <v>8.5</v>
       </c>
       <c r="I4" s="1">
-        <v>18.649999999999999</v>
+        <v>11.19</v>
       </c>
       <c r="J4" s="1">
         <v>30</v>
@@ -889,7 +889,7 @@
         <v>22.7</v>
       </c>
       <c r="I5" s="1">
-        <v>0.67</v>
+        <v>0.4</v>
       </c>
       <c r="J5" s="1">
         <v>10</v>
@@ -936,7 +936,7 @@
         <v>14</v>
       </c>
       <c r="I6" s="1">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="J6" s="1">
         <v>13</v>

--- a/Assets/06 Data/ExcelData/dt_gun_item.xlsx
+++ b/Assets/06 Data/ExcelData/dt_gun_item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Genie\Desktop\duckov-clone\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29524B82-8F2F-419A-8958-2DD8153567CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDFFAA5-AD1A-4688-83DC-70578A8967E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4185" windowWidth="24300" windowHeight="11295" xr2:uid="{818AEAD1-047B-4735-8CBD-03FE823548AF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{818AEAD1-047B-4735-8CBD-03FE823548AF}"/>
   </bookViews>
   <sheets>
     <sheet name="무기" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
   <si>
     <t>가치</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -199,6 +199,18 @@
   </si>
   <si>
     <t>SoundRange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 연발 수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnemyFireCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -265,7 +277,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -288,13 +300,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -308,6 +331,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -655,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67FC45F5-0ACC-4C1F-9F62-F8E7255584F7}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.75" style="1" bestFit="1" customWidth="1"/>
@@ -672,10 +704,11 @@
     <col min="12" max="12" width="13.875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.75" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
@@ -721,8 +754,11 @@
       <c r="O1" s="4" t="s">
         <v>39</v>
       </c>
+      <c r="P1" s="5" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -768,8 +804,11 @@
       <c r="O2" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="P2" s="6" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -815,8 +854,11 @@
       <c r="O3" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="P3" s="7" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>258</v>
       </c>
@@ -862,8 +904,11 @@
       <c r="O4" s="1">
         <v>20.3</v>
       </c>
+      <c r="P4" s="1">
+        <v>6</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>780</v>
       </c>
@@ -909,8 +954,11 @@
       <c r="O5" s="1">
         <v>24.6</v>
       </c>
+      <c r="P5" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>254</v>
       </c>
@@ -955,6 +1003,9 @@
       </c>
       <c r="O6" s="1">
         <v>41.7</v>
+      </c>
+      <c r="P6" s="1">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/06 Data/ExcelData/dt_gun_item.xlsx
+++ b/Assets/06 Data/ExcelData/dt_gun_item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Genie\Desktop\duckov-clone\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDFFAA5-AD1A-4688-83DC-70578A8967E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8EB011A-C509-47E1-BEC1-B272ECE1DE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{818AEAD1-047B-4735-8CBD-03FE823548AF}"/>
+    <workbookView xWindow="6750" yWindow="2775" windowWidth="20595" windowHeight="11295" xr2:uid="{818AEAD1-047B-4735-8CBD-03FE823548AF}"/>
   </bookViews>
   <sheets>
     <sheet name="무기" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
   <si>
     <t>가치</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -67,10 +67,6 @@
   </si>
   <si>
     <t>S</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>uint</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -710,19 +706,19 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>0</v>
@@ -743,119 +739,119 @@
         <v>5</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="O2" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="J3" s="3" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
@@ -863,10 +859,10 @@
         <v>258</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
@@ -913,16 +909,16 @@
         <v>780</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="F5" s="1">
         <v>8767</v>
@@ -963,13 +959,13 @@
         <v>254</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>7</v>

--- a/Assets/06 Data/ExcelData/dt_gun_item.xlsx
+++ b/Assets/06 Data/ExcelData/dt_gun_item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Genie\Desktop\duckov-clone\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8EB011A-C509-47E1-BEC1-B272ECE1DE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3DCCD5-7FBF-4E48-88E2-6A06F0590F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6750" yWindow="2775" windowWidth="20595" windowHeight="11295" xr2:uid="{818AEAD1-047B-4735-8CBD-03FE823548AF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{818AEAD1-047B-4735-8CBD-03FE823548AF}"/>
   </bookViews>
   <sheets>
     <sheet name="무기" sheetId="1" r:id="rId1"/>
@@ -901,7 +901,7 @@
         <v>20.3</v>
       </c>
       <c r="P4" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
@@ -930,7 +930,7 @@
         <v>22.7</v>
       </c>
       <c r="I5" s="1">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J5" s="1">
         <v>10</v>

--- a/Assets/06 Data/ExcelData/dt_gun_item.xlsx
+++ b/Assets/06 Data/ExcelData/dt_gun_item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Genie\Desktop\duckov-clone\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3DCCD5-7FBF-4E48-88E2-6A06F0590F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE51D8C-A826-4921-97FE-925D8087FC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{818AEAD1-047B-4735-8CBD-03FE823548AF}"/>
+    <workbookView xWindow="4065" yWindow="3090" windowWidth="20595" windowHeight="11295" xr2:uid="{818AEAD1-047B-4735-8CBD-03FE823548AF}"/>
   </bookViews>
   <sheets>
     <sheet name="무기" sheetId="1" r:id="rId1"/>
@@ -898,7 +898,7 @@
         <v>1</v>
       </c>
       <c r="O4" s="1">
-        <v>20.3</v>
+        <v>41.7</v>
       </c>
       <c r="P4" s="1">
         <v>5</v>
@@ -998,7 +998,7 @@
         <v>1</v>
       </c>
       <c r="O6" s="1">
-        <v>41.7</v>
+        <v>20.3</v>
       </c>
       <c r="P6" s="1">
         <v>4</v>

--- a/Assets/06 Data/ExcelData/dt_gun_item.xlsx
+++ b/Assets/06 Data/ExcelData/dt_gun_item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Genie\Desktop\duckov-clone\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE51D8C-A826-4921-97FE-925D8087FC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5CED13-9F92-413A-BAA8-0FC96F4C5AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4065" yWindow="3090" windowWidth="20595" windowHeight="11295" xr2:uid="{818AEAD1-047B-4735-8CBD-03FE823548AF}"/>
   </bookViews>
@@ -880,7 +880,7 @@
         <v>8.5</v>
       </c>
       <c r="I4" s="1">
-        <v>11.19</v>
+        <v>9.5</v>
       </c>
       <c r="J4" s="1">
         <v>30</v>
